--- a/data_out/country_spreadsheets/Ireland.xlsx
+++ b/data_out/country_spreadsheets/Ireland.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>132.65</v>
       </c>
+      <c r="X2" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>105.06</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>114.58</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>132.65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>139.59</v>
       </c>
+      <c r="X3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>165.16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>87.48</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>127.69</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>130.33</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>37.46</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>152.32</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>139.59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>192.98</v>
       </c>
+      <c r="X4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>173.21</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>120.64</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>220.61</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>192.98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>170.27</v>
       </c>
+      <c r="X5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>130.67</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>66.27</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>223.23</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>170.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>148.88</v>
       </c>
+      <c r="X6" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>67</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>147.28</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>207.44</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>148.88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>191.11</v>
       </c>
+      <c r="X7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>229.92</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>202.96</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>67.03</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>225</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>191.11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>203.92</v>
       </c>
+      <c r="X8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>158.39</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>186.23</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>224.65</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>203.92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1158,6 +1600,57 @@
         <v>37.32</v>
       </c>
       <c r="W9" t="n">
+        <v>168.37</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>34.94</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>95.03</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>182.59</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>114.61</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>125.01</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="AN9" t="n">
         <v>168.37</v>
       </c>
     </row>
